--- a/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
   </si>
   <si>
     <t>Version</t>

--- a/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Dental BodyStructure ValueSet</t>
+    <t>JP Core Dental Surface BodyStructure ValueSet</t>
   </si>
   <si>
     <t>Status</t>

--- a/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/ValueSet-jp-dental-surfacebodystructure-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Dental Surface BodyStructure ValueSet</t>
+    <t>JP Core Dental SurfaceBodyStructure ValueSet</t>
   </si>
   <si>
     <t>Status</t>
